--- a/Ecommerce.xlsx
+++ b/Ecommerce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Power-BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C63B29C-09BE-4014-A370-69BE3B9986FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF4FAFB-B9C0-413B-B7E0-617F4C7962B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{671AF70F-F366-434C-9500-DCB6FBEC178A}"/>
   </bookViews>
@@ -3347,6 +3347,9 @@
       <c r="C6" s="1">
         <v>45670</v>
       </c>
+      <c r="D6" s="1">
+        <v>45672</v>
+      </c>
       <c r="E6" t="s">
         <v>237</v>
       </c>
@@ -3428,6 +3431,12 @@
       <c r="B9" t="s">
         <v>103</v>
       </c>
+      <c r="C9" s="1">
+        <v>45677</v>
+      </c>
+      <c r="D9" s="1">
+        <v>45681</v>
+      </c>
       <c r="E9" t="s">
         <v>237</v>
       </c>
@@ -3512,6 +3521,9 @@
       <c r="C12" s="1">
         <v>45691</v>
       </c>
+      <c r="D12" s="1">
+        <v>45687</v>
+      </c>
       <c r="E12" t="s">
         <v>237</v>
       </c>
@@ -3711,6 +3723,9 @@
       </c>
       <c r="C19" s="1">
         <v>45712</v>
+      </c>
+      <c r="D19" s="1">
+        <v>45713</v>
       </c>
       <c r="E19" t="s">
         <v>237</v>

--- a/Ecommerce.xlsx
+++ b/Ecommerce.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Power-BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF4FAFB-B9C0-413B-B7E0-617F4C7962B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A8F4EE-DFF3-4246-9DCD-E55E2020C8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{671AF70F-F366-434C-9500-DCB6FBEC178A}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="246">
   <si>
     <t>CustomerID</t>
   </si>
@@ -211,9 +211,6 @@
     <t>Lucknow</t>
   </si>
   <si>
-    <t>Uttar Pradesh</t>
-  </si>
-  <si>
     <t>C013</t>
   </si>
   <si>
@@ -223,9 +220,6 @@
     <t>Indore</t>
   </si>
   <si>
-    <t>Madhya Pradesh</t>
-  </si>
-  <si>
     <t>C014</t>
   </si>
   <si>
@@ -253,9 +247,6 @@
     <t>Amritsar</t>
   </si>
   <si>
-    <t>Punjab</t>
-  </si>
-  <si>
     <t>C017</t>
   </si>
   <si>
@@ -280,9 +271,6 @@
     <t>Kolkata</t>
   </si>
   <si>
-    <t>West Bengal</t>
-  </si>
-  <si>
     <t>C020</t>
   </si>
   <si>
@@ -460,9 +448,6 @@
     <t>Laptop Backpack</t>
   </si>
   <si>
-    <t>Bags</t>
-  </si>
-  <si>
     <t>Skybags</t>
   </si>
   <si>
@@ -472,9 +457,6 @@
     <t>Fashion</t>
   </si>
   <si>
-    <t>Footwear</t>
-  </si>
-  <si>
     <t>Nike</t>
   </si>
   <si>
@@ -523,12 +505,6 @@
     <t>Office Chair</t>
   </si>
   <si>
-    <t>Furniture</t>
-  </si>
-  <si>
-    <t>Chairs</t>
-  </si>
-  <si>
     <t>Featherlite</t>
   </si>
   <si>
@@ -538,9 +514,6 @@
     <t>Study Table</t>
   </si>
   <si>
-    <t>Tables</t>
-  </si>
-  <si>
     <t>Wakefit</t>
   </si>
   <si>
@@ -595,45 +568,18 @@
     <t>P017</t>
   </si>
   <si>
-    <t>Smartphone</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
     <t>Samsung</t>
   </si>
   <si>
     <t>P018</t>
   </si>
   <si>
-    <t>Power Bank</t>
-  </si>
-  <si>
-    <t>Mi</t>
-  </si>
-  <si>
     <t>P019</t>
   </si>
   <si>
-    <t>LED Monitor</t>
-  </si>
-  <si>
-    <t>Computers</t>
-  </si>
-  <si>
-    <t>Dell</t>
-  </si>
-  <si>
     <t>P020</t>
   </si>
   <si>
-    <t>USB-C Cable</t>
-  </si>
-  <si>
-    <t>Anker</t>
-  </si>
-  <si>
     <t>PaymentID</t>
   </si>
   <si>
@@ -818,6 +764,21 @@
   </si>
   <si>
     <t>SHP020</t>
+  </si>
+  <si>
+    <t>Helmet</t>
+  </si>
+  <si>
+    <t>Studds</t>
+  </si>
+  <si>
+    <t>Cricket Ball</t>
+  </si>
+  <si>
+    <t>Sweat T-Shirt</t>
+  </si>
+  <si>
+    <t>Hanix</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1220,7 @@
         <v>19</v>
       </c>
       <c r="H3" s="1">
-        <v>45332</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1305,13 +1266,13 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="1">
-        <v>45371</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1357,13 +1318,13 @@
         <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="1">
-        <v>45420</v>
+        <v>45785</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1383,7 +1344,7 @@
         <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
@@ -1409,13 +1370,13 @@
         <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>43</v>
       </c>
       <c r="H9" s="1">
-        <v>45453</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1461,13 +1422,13 @@
         <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
       <c r="H11" s="1">
-        <v>45488</v>
+        <v>45853</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1487,7 +1448,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
@@ -1513,21 +1474,21 @@
         <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>43</v>
       </c>
       <c r="H13" s="1">
-        <v>45524</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
@@ -1536,10 +1497,10 @@
         <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -1550,13 +1511,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
         <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
       </c>
       <c r="D15">
         <v>29</v>
@@ -1565,21 +1526,21 @@
         <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>19</v>
       </c>
       <c r="H15" s="1">
-        <v>45550</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
@@ -1588,10 +1549,10 @@
         <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1602,36 +1563,36 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17">
         <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
         <v>43</v>
       </c>
       <c r="H17" s="1">
-        <v>45583</v>
+        <v>45948</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
@@ -1640,7 +1601,7 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -1654,13 +1615,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19">
         <v>31</v>
@@ -1669,21 +1630,21 @@
         <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
         <v>19</v>
       </c>
       <c r="H19" s="1">
-        <v>45611</v>
+        <v>45976</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -1692,10 +1653,10 @@
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="G20" t="s">
         <v>43</v>
@@ -1706,10 +1667,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
         <v>16</v>
@@ -1721,13 +1682,13 @@
         <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21" s="1">
-        <v>45636</v>
+        <v>46001</v>
       </c>
     </row>
   </sheetData>
@@ -1751,42 +1712,42 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" t="s">
         <v>120</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>121</v>
-      </c>
-      <c r="D1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F2">
         <v>450</v>
@@ -1797,19 +1758,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" t="s">
         <v>127</v>
-      </c>
-      <c r="D3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" t="s">
-        <v>131</v>
       </c>
       <c r="F3">
         <v>1800</v>
@@ -1820,19 +1781,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F4">
         <v>900</v>
@@ -1843,19 +1804,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F5">
         <v>2200</v>
@@ -1866,19 +1827,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F6">
         <v>800</v>
@@ -1889,19 +1850,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F7">
         <v>2500</v>
@@ -1912,19 +1873,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F8">
         <v>500</v>
@@ -1935,19 +1896,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F9">
         <v>1200</v>
@@ -1958,19 +1919,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F10">
         <v>1800</v>
@@ -1981,19 +1942,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F11">
         <v>900</v>
@@ -2004,19 +1965,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F12">
         <v>5500</v>
@@ -2027,19 +1988,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F13">
         <v>4000</v>
@@ -2050,19 +2011,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F14">
         <v>300</v>
@@ -2073,19 +2034,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F15">
         <v>500</v>
@@ -2096,19 +2057,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E16" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="F16">
         <v>1800</v>
@@ -2119,19 +2080,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" t="s">
         <v>173</v>
-      </c>
-      <c r="D17" t="s">
-        <v>181</v>
-      </c>
-      <c r="E17" t="s">
-        <v>182</v>
       </c>
       <c r="F17">
         <v>600</v>
@@ -2142,19 +2103,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B18" t="s">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="F18">
         <v>15000</v>
@@ -2165,19 +2126,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B19" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="F19">
         <v>900</v>
@@ -2188,19 +2149,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="D20" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="F20">
         <v>7000</v>
@@ -2211,19 +2172,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="F21">
         <v>400</v>
@@ -2252,30 +2213,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1">
         <v>45662</v>
@@ -2284,7 +2245,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -2293,12 +2254,12 @@
         <v>0.05</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B3" s="1">
         <v>45663</v>
@@ -2307,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2316,12 +2277,12 @@
         <v>0.1</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B4" s="1">
         <v>45665</v>
@@ -2330,7 +2291,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2339,12 +2300,12 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B5" s="1">
         <v>45667</v>
@@ -2353,7 +2314,7 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -2362,12 +2323,12 @@
         <v>0.15</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B6" s="1">
         <v>45669</v>
@@ -2376,7 +2337,7 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -2385,12 +2346,12 @@
         <v>0.05</v>
       </c>
       <c r="G6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B7" s="1">
         <v>45672</v>
@@ -2399,7 +2360,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2408,12 +2369,12 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B8" s="1">
         <v>45675</v>
@@ -2422,7 +2383,7 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2431,12 +2392,12 @@
         <v>0.1</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B9" s="1">
         <v>45677</v>
@@ -2445,7 +2406,7 @@
         <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -2454,12 +2415,12 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B10" s="1">
         <v>45679</v>
@@ -2468,7 +2429,7 @@
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -2477,12 +2438,12 @@
         <v>0.05</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B11" s="1">
         <v>45682</v>
@@ -2491,7 +2452,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2500,12 +2461,12 @@
         <v>0.1</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B12" s="1">
         <v>45690</v>
@@ -2514,7 +2475,7 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -2523,12 +2484,12 @@
         <v>0.15</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B13" s="1">
         <v>45693</v>
@@ -2537,7 +2498,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2546,12 +2507,12 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B14" s="1">
         <v>45696</v>
@@ -2560,7 +2521,7 @@
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2569,12 +2530,12 @@
         <v>0.2</v>
       </c>
       <c r="G14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1">
         <v>45698</v>
@@ -2583,7 +2544,7 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2592,12 +2553,12 @@
         <v>0.05</v>
       </c>
       <c r="G15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B16" s="1">
         <v>45702</v>
@@ -2606,7 +2567,7 @@
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2615,12 +2576,12 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B17" s="1">
         <v>45706</v>
@@ -2629,7 +2590,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -2638,12 +2599,12 @@
         <v>0.1</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B18" s="1">
         <v>45708</v>
@@ -2652,7 +2613,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2661,12 +2622,12 @@
         <v>0.15</v>
       </c>
       <c r="G18" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B19" s="1">
         <v>45711</v>
@@ -2675,7 +2636,7 @@
         <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -2684,12 +2645,12 @@
         <v>0.05</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B20" s="1">
         <v>45714</v>
@@ -2698,7 +2659,7 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2707,12 +2668,12 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B21" s="1">
         <v>45716</v>
@@ -2721,7 +2682,7 @@
         <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2730,7 +2691,7 @@
         <v>0.1</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2753,39 +2714,39 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="D1" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="E1" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="F1" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1">
-        <v>45662</v>
+        <v>45296</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F2">
         <v>1330</v>
@@ -2793,19 +2754,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1">
         <v>45663</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F3">
         <v>1350</v>
@@ -2813,19 +2774,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1">
-        <v>45665</v>
+        <v>45299</v>
       </c>
       <c r="D4" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F4">
         <v>8400</v>
@@ -2833,19 +2794,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1">
         <v>45667</v>
       </c>
       <c r="D5" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E5" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F5">
         <v>1190</v>
@@ -2853,19 +2814,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1">
-        <v>45669</v>
+        <v>45303</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E6" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F6">
         <v>6650</v>
@@ -2873,19 +2834,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C7" s="1">
         <v>45672</v>
       </c>
       <c r="D7" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="E7" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F7">
         <v>1500</v>
@@ -2893,19 +2854,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1">
-        <v>45675</v>
+        <v>45309</v>
       </c>
       <c r="D8" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E8" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F8">
         <v>3780</v>
@@ -2913,19 +2874,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1">
         <v>45677</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="F9">
         <v>1995</v>
@@ -2933,19 +2894,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="1">
-        <v>45679</v>
+        <v>45313</v>
       </c>
       <c r="D10" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E10" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F10">
         <v>1710</v>
@@ -2953,19 +2914,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1">
         <v>45682</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="E11" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F11">
         <v>3150</v>
@@ -2973,19 +2934,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1">
-        <v>45690</v>
+        <v>45324</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F12">
         <v>2380</v>
@@ -2993,19 +2954,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C13" s="1">
         <v>45693</v>
       </c>
       <c r="D13" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E13" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F13">
         <v>2800</v>
@@ -3013,19 +2974,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C14" s="1">
-        <v>45696</v>
+        <v>45330</v>
       </c>
       <c r="D14" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E14" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F14">
         <v>3520</v>
@@ -3033,19 +2994,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C15" s="1">
         <v>45698</v>
       </c>
       <c r="D15" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="E15" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F15">
         <v>3990</v>
@@ -3053,19 +3014,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C16" s="1">
-        <v>45702</v>
+        <v>45336</v>
       </c>
       <c r="D16" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E16" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="F16">
         <v>2700</v>
@@ -3073,19 +3034,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C17" s="1">
         <v>45706</v>
       </c>
       <c r="D17" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="E17" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F17">
         <v>2700</v>
@@ -3093,19 +3054,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C18" s="1">
-        <v>45708</v>
+        <v>45342</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E18" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F18">
         <v>1870</v>
@@ -3113,19 +3074,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C19" s="1">
         <v>45711</v>
       </c>
       <c r="D19" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E19" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F19">
         <v>1330</v>
@@ -3133,19 +3094,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C20" s="1">
-        <v>45714</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="E20" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F20">
         <v>3500</v>
@@ -3153,19 +3114,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C21" s="1">
         <v>45716</v>
       </c>
       <c r="D21" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F21">
         <v>2520</v>
@@ -3194,48 +3155,48 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="D1" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="E1" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="F1" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="G1" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="H1" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="I1" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1">
-        <v>45663</v>
+        <v>45297</v>
       </c>
       <c r="D2" s="1">
-        <v>45666</v>
+        <v>45300</v>
       </c>
       <c r="E2" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -3244,7 +3205,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I2">
         <v>80</v>
@@ -3252,10 +3213,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1">
         <v>45664</v>
@@ -3264,7 +3225,7 @@
         <v>45667</v>
       </c>
       <c r="E3" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="F3" t="s">
         <v>17</v>
@@ -3273,7 +3234,7 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I3">
         <v>120</v>
@@ -3281,19 +3242,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1">
-        <v>45666</v>
+        <v>45300</v>
       </c>
       <c r="D4" s="1">
-        <v>45670</v>
+        <v>45304</v>
       </c>
       <c r="E4" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
@@ -3302,7 +3263,7 @@
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3310,10 +3271,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1">
         <v>45668</v>
@@ -3322,7 +3283,7 @@
         <v>45671</v>
       </c>
       <c r="E5" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
@@ -3331,7 +3292,7 @@
         <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I5">
         <v>150</v>
@@ -3339,19 +3300,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1">
-        <v>45670</v>
+        <v>45304</v>
       </c>
       <c r="D6" s="1">
-        <v>45672</v>
+        <v>45306</v>
       </c>
       <c r="E6" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -3360,7 +3321,7 @@
         <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -3368,10 +3329,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C7" s="1">
         <v>45673</v>
@@ -3380,7 +3341,7 @@
         <v>45676</v>
       </c>
       <c r="E7" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -3389,7 +3350,7 @@
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I7">
         <v>80</v>
@@ -3397,19 +3358,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1">
-        <v>45676</v>
+        <v>45310</v>
       </c>
       <c r="D8" s="1">
-        <v>45680</v>
+        <v>45314</v>
       </c>
       <c r="E8" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F8" t="s">
         <v>33</v>
@@ -3418,7 +3379,7 @@
         <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I8">
         <v>110</v>
@@ -3426,10 +3387,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1">
         <v>45677</v>
@@ -3438,7 +3399,7 @@
         <v>45681</v>
       </c>
       <c r="E9" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="F9" t="s">
         <v>37</v>
@@ -3447,7 +3408,7 @@
         <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3455,19 +3416,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="1">
-        <v>45680</v>
+        <v>45314</v>
       </c>
       <c r="D10" s="1">
-        <v>45683</v>
+        <v>45317</v>
       </c>
       <c r="E10" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="F10" t="s">
         <v>41</v>
@@ -3476,7 +3437,7 @@
         <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I10">
         <v>140</v>
@@ -3484,10 +3445,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1">
         <v>45683</v>
@@ -3496,7 +3457,7 @@
         <v>45686</v>
       </c>
       <c r="E11" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
@@ -3505,7 +3466,7 @@
         <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I11">
         <v>90</v>
@@ -3513,19 +3474,19 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1">
-        <v>45691</v>
+        <v>45325</v>
       </c>
       <c r="D12" s="1">
-        <v>45687</v>
+        <v>45321</v>
       </c>
       <c r="E12" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F12" t="s">
         <v>23</v>
@@ -3534,7 +3495,7 @@
         <v>12</v>
       </c>
       <c r="H12" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -3542,10 +3503,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C13" s="1">
         <v>45694</v>
@@ -3554,7 +3515,7 @@
         <v>45697</v>
       </c>
       <c r="E13" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="F13" t="s">
         <v>46</v>
@@ -3563,7 +3524,7 @@
         <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I13">
         <v>130</v>
@@ -3571,19 +3532,19 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C14" s="1">
-        <v>45697</v>
+        <v>45331</v>
       </c>
       <c r="D14" s="1">
-        <v>45701</v>
+        <v>45335</v>
       </c>
       <c r="E14" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F14" t="s">
         <v>49</v>
@@ -3592,7 +3553,7 @@
         <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I14">
         <v>110</v>
@@ -3600,10 +3561,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C15" s="1">
         <v>45699</v>
@@ -3612,7 +3573,7 @@
         <v>45703</v>
       </c>
       <c r="E15" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
@@ -3621,7 +3582,7 @@
         <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -3629,19 +3590,19 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C16" s="1">
-        <v>45703</v>
+        <v>45337</v>
       </c>
       <c r="D16" s="1">
-        <v>45706</v>
+        <v>45340</v>
       </c>
       <c r="E16" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
@@ -3650,7 +3611,7 @@
         <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -3658,10 +3619,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C17" s="1">
         <v>45707</v>
@@ -3670,7 +3631,7 @@
         <v>45710</v>
       </c>
       <c r="E17" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="F17" t="s">
         <v>33</v>
@@ -3679,7 +3640,7 @@
         <v>34</v>
       </c>
       <c r="H17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I17">
         <v>130</v>
@@ -3687,19 +3648,19 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C18" s="1">
-        <v>45709</v>
+        <v>45343</v>
       </c>
       <c r="D18" s="1">
-        <v>45712</v>
+        <v>45346</v>
       </c>
       <c r="E18" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F18" t="s">
         <v>37</v>
@@ -3708,7 +3669,7 @@
         <v>38</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -3716,10 +3677,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C19" s="1">
         <v>45712</v>
@@ -3728,7 +3689,7 @@
         <v>45713</v>
       </c>
       <c r="E19" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="F19" t="s">
         <v>41</v>
@@ -3737,7 +3698,7 @@
         <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="I19">
         <v>90</v>
@@ -3745,19 +3706,19 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C20" s="1">
-        <v>45715</v>
+        <v>45349</v>
       </c>
       <c r="D20" s="1">
-        <v>45718</v>
+        <v>45353</v>
       </c>
       <c r="E20" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
@@ -3766,7 +3727,7 @@
         <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -3774,10 +3735,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C21" s="1">
         <v>45717</v>
@@ -3786,7 +3747,7 @@
         <v>45720</v>
       </c>
       <c r="E21" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="F21" t="s">
         <v>49</v>
@@ -3795,7 +3756,7 @@
         <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I21">
         <v>140</v>

--- a/Ecommerce.xlsx
+++ b/Ecommerce.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\Power-BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A8F4EE-DFF3-4246-9DCD-E55E2020C8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF6A97C-5B20-4AD0-8F9F-F3346FCCA834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{671AF70F-F366-434C-9500-DCB6FBEC178A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{671AF70F-F366-434C-9500-DCB6FBEC178A}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="231">
   <si>
     <t>CustomerID</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Aarav Sharma</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>Mumbai</t>
   </si>
   <si>
@@ -121,9 +118,6 @@
     <t>Priya Singh</t>
   </si>
   <si>
-    <t>Delhi</t>
-  </si>
-  <si>
     <t>C005</t>
   </si>
   <si>
@@ -142,36 +136,18 @@
     <t>Neha Joshi</t>
   </si>
   <si>
-    <t>Jaipur</t>
-  </si>
-  <si>
-    <t>Rajasthan</t>
-  </si>
-  <si>
     <t>C007</t>
   </si>
   <si>
     <t>Arjun Nair</t>
   </si>
   <si>
-    <t>Kochi</t>
-  </si>
-  <si>
-    <t>Kerala</t>
-  </si>
-  <si>
     <t>C008</t>
   </si>
   <si>
     <t>Ishita Rao</t>
   </si>
   <si>
-    <t>Hyderabad</t>
-  </si>
-  <si>
-    <t>Telangana</t>
-  </si>
-  <si>
     <t>New</t>
   </si>
   <si>
@@ -190,12 +166,6 @@
     <t>Meera Iyer</t>
   </si>
   <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>Tamil Nadu</t>
-  </si>
-  <si>
     <t>C011</t>
   </si>
   <si>
@@ -208,45 +178,30 @@
     <t>Sneha Kapoor</t>
   </si>
   <si>
-    <t>Lucknow</t>
-  </si>
-  <si>
     <t>C013</t>
   </si>
   <si>
     <t>Aditya Verma</t>
   </si>
   <si>
-    <t>Indore</t>
-  </si>
-  <si>
     <t>C014</t>
   </si>
   <si>
     <t>Kavya Reddy</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>C015</t>
   </si>
   <si>
     <t>Manish Gupta</t>
   </si>
   <si>
-    <t>Noida</t>
-  </si>
-  <si>
     <t>C016</t>
   </si>
   <si>
     <t>Simran Kaur</t>
   </si>
   <si>
-    <t>Amritsar</t>
-  </si>
-  <si>
     <t>C017</t>
   </si>
   <si>
@@ -268,9 +223,6 @@
     <t>Dev Agarwal</t>
   </si>
   <si>
-    <t>Kolkata</t>
-  </si>
-  <si>
     <t>C020</t>
   </si>
   <si>
@@ -433,9 +385,6 @@
     <t>Audio</t>
   </si>
   <si>
-    <t>Boat</t>
-  </si>
-  <si>
     <t>Smart Watch</t>
   </si>
   <si>
@@ -472,9 +421,6 @@
     <t>Denim Jeans</t>
   </si>
   <si>
-    <t>Levis</t>
-  </si>
-  <si>
     <t>P009</t>
   </si>
   <si>
@@ -523,9 +469,6 @@
     <t>Water Bottle</t>
   </si>
   <si>
-    <t>Kitchen</t>
-  </si>
-  <si>
     <t>Milton</t>
   </si>
   <si>
@@ -568,9 +511,6 @@
     <t>P017</t>
   </si>
   <si>
-    <t>Samsung</t>
-  </si>
-  <si>
     <t>P018</t>
   </si>
   <si>
@@ -779,13 +719,28 @@
   </si>
   <si>
     <t>Hanix</t>
+  </si>
+  <si>
+    <t>boAt</t>
+  </si>
+  <si>
+    <t>Bags</t>
+  </si>
+  <si>
+    <t>Footwear</t>
+  </si>
+  <si>
+    <t>Levi's</t>
+  </si>
+  <si>
+    <t>Furniture</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -793,13 +748,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0D0D0D"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFCFC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -814,10 +781,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1146,7 +1119,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1172,520 +1145,520 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>28</v>
       </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
       </c>
       <c r="H2" s="1">
         <v>45306</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
       </c>
       <c r="D3">
         <v>32</v>
       </c>
       <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
       </c>
       <c r="H3" s="1">
         <v>45698</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
       </c>
       <c r="D4">
         <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
         <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
       </c>
       <c r="H4" s="1">
         <v>45356</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" s="1">
         <v>45736</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
+      <c r="A6" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H6" s="1">
         <v>45394</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>31</v>
+      <c r="A7" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" s="1">
         <v>45785</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>35</v>
+      <c r="A8" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8" s="1">
         <v>45437</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>39</v>
+      <c r="A9" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H9" s="1">
         <v>45818</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
+      <c r="A10" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
         <v>18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
       </c>
       <c r="H10" s="1">
         <v>45474</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>47</v>
+      <c r="A11" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" s="1">
         <v>45853</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>51</v>
+      <c r="A12" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" s="1">
         <v>45509</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>53</v>
+      <c r="A13" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1">
         <v>45889</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>56</v>
+      <c r="A14" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14">
         <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" t="s">
         <v>12</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
       <c r="H14" s="1">
         <v>45536</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>59</v>
+      <c r="A15" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H15" s="1">
         <v>45915</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>62</v>
+      <c r="A16" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16">
         <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" t="s">
         <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
       </c>
       <c r="H16" s="1">
         <v>45566</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>65</v>
+      <c r="A17" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1">
         <v>45948</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>68</v>
+      <c r="A18" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="1">
         <v>45598</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>71</v>
+      <c r="A19" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" s="1">
         <v>45976</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>73</v>
+      <c r="A20" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20">
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H20" s="1">
         <v>45627</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>76</v>
+      <c r="A21" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H21" s="1">
         <v>46001</v>
@@ -1693,6 +1666,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1711,43 +1685,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>80</v>
+      <c r="A1" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E1" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="F1" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G1" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>85</v>
+      <c r="A2" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="F2">
         <v>450</v>
@@ -1757,20 +1731,20 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>90</v>
+      <c r="A3" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="F3">
         <v>1800</v>
@@ -1780,20 +1754,20 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>88</v>
+      <c r="A4" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>130</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>900</v>
@@ -1803,20 +1777,20 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>94</v>
+      <c r="A5" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F5">
         <v>2200</v>
@@ -1826,20 +1800,20 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>92</v>
+      <c r="A6" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="F6">
         <v>800</v>
@@ -1849,20 +1823,20 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>98</v>
+      <c r="A7" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F7">
         <v>2500</v>
@@ -1872,20 +1846,20 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>102</v>
+      <c r="A8" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="F8">
         <v>500</v>
@@ -1895,20 +1869,20 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>107</v>
+      <c r="A9" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="F9">
         <v>1200</v>
@@ -1918,20 +1892,20 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>144</v>
+      <c r="A10" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="F10">
         <v>1800</v>
@@ -1941,20 +1915,20 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>149</v>
+      <c r="A11" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F11">
         <v>900</v>
@@ -1964,20 +1938,20 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>152</v>
+      <c r="A12" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>230</v>
       </c>
       <c r="E12" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="F12">
         <v>5500</v>
@@ -1987,20 +1961,20 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>155</v>
+      <c r="A13" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" t="s">
         <v>146</v>
       </c>
-      <c r="D13" t="s">
-        <v>147</v>
-      </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F13">
         <v>4000</v>
@@ -2010,20 +1984,20 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>158</v>
+      <c r="A14" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="F14">
         <v>300</v>
@@ -2033,20 +2007,20 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>162</v>
+      <c r="A15" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="C15" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="F15">
         <v>500</v>
@@ -2056,20 +2030,20 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>167</v>
+      <c r="A16" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="F16">
         <v>1800</v>
@@ -2079,20 +2053,20 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>171</v>
+      <c r="A17" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="C17" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="F17">
         <v>600</v>
@@ -2102,43 +2076,43 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>174</v>
+      <c r="A18" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="B18" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="C18" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="F18">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="G18">
-        <v>22000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>176</v>
+      <c r="A19" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="B19" t="s">
-        <v>242</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F19">
         <v>900</v>
@@ -2148,43 +2122,43 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>177</v>
+      <c r="A20" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="F20">
-        <v>7000</v>
+        <v>700</v>
       </c>
       <c r="G20">
-        <v>10500</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>178</v>
+      <c r="A21" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="F21">
         <v>400</v>
@@ -2195,6 +2169,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2212,40 +2187,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>78</v>
+      <c r="A1" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>84</v>
+      <c r="A2" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B2" s="1">
-        <v>45662</v>
+        <v>45296</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -2254,21 +2229,21 @@
         <v>0.05</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>87</v>
+      <c r="A3" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B3" s="1">
-        <v>45663</v>
+        <v>45297</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2277,21 +2252,21 @@
         <v>0.1</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>89</v>
+      <c r="A4" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B4" s="1">
-        <v>45665</v>
+        <v>45299</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2300,21 +2275,21 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>91</v>
+      <c r="A5" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B5" s="1">
-        <v>45667</v>
+        <v>45301</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -2323,21 +2298,21 @@
         <v>0.15</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>93</v>
+      <c r="A6" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B6" s="1">
-        <v>45669</v>
+        <v>45303</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -2346,21 +2321,21 @@
         <v>0.05</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>96</v>
+      <c r="A7" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B7" s="1">
-        <v>45672</v>
+        <v>45306</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2369,21 +2344,21 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>97</v>
+      <c r="A8" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="B8" s="1">
-        <v>45675</v>
+        <v>45309</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2392,21 +2367,21 @@
         <v>0.1</v>
       </c>
       <c r="G8" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>99</v>
+      <c r="A9" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B9" s="1">
-        <v>45677</v>
+        <v>45311</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -2415,21 +2390,21 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>101</v>
+      <c r="A10" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B10" s="1">
-        <v>45679</v>
+        <v>45313</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -2438,21 +2413,21 @@
         <v>0.05</v>
       </c>
       <c r="G10" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>103</v>
+      <c r="A11" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="B11" s="1">
-        <v>45682</v>
+        <v>45316</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2461,21 +2436,21 @@
         <v>0.1</v>
       </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>104</v>
+      <c r="A12" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>45690</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -2484,21 +2459,21 @@
         <v>0.15</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>105</v>
+      <c r="A13" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="B13" s="1">
         <v>45693</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2507,21 +2482,21 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>106</v>
+      <c r="A14" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B14" s="1">
         <v>45696</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2530,21 +2505,21 @@
         <v>0.2</v>
       </c>
       <c r="G14" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>108</v>
+      <c r="A15" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B15" s="1">
         <v>45698</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2553,21 +2528,21 @@
         <v>0.05</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>109</v>
+      <c r="A16" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B16" s="1">
         <v>45702</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2576,21 +2551,21 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>111</v>
+      <c r="A17" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B17" s="1">
         <v>45706</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -2599,21 +2574,21 @@
         <v>0.1</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>112</v>
+      <c r="A18" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="B18" s="1">
         <v>45708</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2622,21 +2597,21 @@
         <v>0.15</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>113</v>
+      <c r="A19" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="B19" s="1">
         <v>45711</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -2645,21 +2620,21 @@
         <v>0.05</v>
       </c>
       <c r="G19" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>114</v>
+      <c r="A20" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="B20" s="1">
         <v>45714</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2668,21 +2643,21 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>115</v>
+      <c r="A21" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="B21" s="1">
         <v>45716</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2691,11 +2666,12 @@
         <v>0.1</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2713,420 +2689,420 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>179</v>
+      <c r="A1" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="E1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="F1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>184</v>
+      <c r="A2" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1">
         <v>45296</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F2">
         <v>1330</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>187</v>
+      <c r="A3" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1">
-        <v>45663</v>
+        <v>45297</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F3">
         <v>1350</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>189</v>
+      <c r="A4" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C4" s="1">
         <v>45299</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F4">
         <v>8400</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>191</v>
+      <c r="A5" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C5" s="1">
-        <v>45667</v>
+        <v>45301</v>
       </c>
       <c r="D5" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F5">
         <v>1190</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>192</v>
+      <c r="A6" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1">
         <v>45303</v>
       </c>
       <c r="D6" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F6">
         <v>6650</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>193</v>
+      <c r="A7" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1">
-        <v>45672</v>
+        <v>45306</v>
       </c>
       <c r="D7" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F7">
         <v>1500</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>195</v>
+      <c r="A8" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C8" s="1">
         <v>45309</v>
       </c>
       <c r="D8" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F8">
         <v>3780</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>196</v>
+      <c r="A9" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1">
-        <v>45677</v>
+        <v>45311</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="F9">
-        <v>1995</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>198</v>
+      <c r="A10" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C10" s="1">
         <v>45313</v>
       </c>
       <c r="D10" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E10" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F10">
         <v>1710</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>199</v>
+      <c r="A11" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1">
-        <v>45682</v>
+        <v>45316</v>
       </c>
       <c r="D11" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F11">
         <v>3150</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>200</v>
+      <c r="A12" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1">
-        <v>45324</v>
+        <v>45690</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E12" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F12">
         <v>2380</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>201</v>
+      <c r="A13" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1">
         <v>45693</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F13">
         <v>2800</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>202</v>
+      <c r="A14" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C14" s="1">
-        <v>45330</v>
+        <v>45696</v>
       </c>
       <c r="D14" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F14">
         <v>3520</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>203</v>
+      <c r="A15" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C15" s="1">
         <v>45698</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E15" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F15">
         <v>3990</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>204</v>
+      <c r="A16" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C16" s="1">
-        <v>45336</v>
+        <v>45702</v>
       </c>
       <c r="D16" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="F16">
         <v>2700</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>205</v>
+      <c r="A17" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C17" s="1">
         <v>45706</v>
       </c>
       <c r="D17" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E17" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F17">
         <v>2700</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>206</v>
+      <c r="A18" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C18" s="1">
-        <v>45342</v>
+        <v>45708</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E18" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F18">
         <v>1870</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>207</v>
+      <c r="A19" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C19" s="1">
         <v>45711</v>
       </c>
       <c r="D19" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F19">
         <v>1330</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>208</v>
+      <c r="A20" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C20" s="1">
-        <v>45348</v>
+        <v>45714</v>
       </c>
       <c r="D20" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F20">
         <v>3500</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>209</v>
+      <c r="A21" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C21" s="1">
         <v>45716</v>
       </c>
       <c r="D21" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F21">
         <v>2520</v>
@@ -3134,6 +3110,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3154,40 +3131,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>210</v>
+      <c r="A1" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="D1" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="E1" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="F1" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="G1" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="H1" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="I1" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>218</v>
+      <c r="A2" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1">
         <v>45297</v>
@@ -3196,56 +3173,56 @@
         <v>45300</v>
       </c>
       <c r="E2" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I2">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>220</v>
+      <c r="A3" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1">
-        <v>45664</v>
+        <v>45298</v>
       </c>
       <c r="D3" s="1">
-        <v>45667</v>
+        <v>45301</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="I3">
         <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>222</v>
+      <c r="A4" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C4" s="1">
         <v>45300</v>
@@ -3254,56 +3231,56 @@
         <v>45304</v>
       </c>
       <c r="E4" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I4">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>223</v>
+      <c r="A5" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C5" s="1">
-        <v>45668</v>
+        <v>45302</v>
       </c>
       <c r="D5" s="1">
-        <v>45671</v>
+        <v>45305</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I5">
         <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>224</v>
+      <c r="A6" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C6" s="1">
         <v>45304</v>
@@ -3312,56 +3289,56 @@
         <v>45306</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>226</v>
+      <c r="A7" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1">
-        <v>45673</v>
+        <v>45307</v>
       </c>
       <c r="D7" s="1">
-        <v>45676</v>
+        <v>45310</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" t="s">
-        <v>12</v>
-      </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I7">
         <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>227</v>
+      <c r="A8" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C8" s="1">
         <v>45310</v>
@@ -3370,56 +3347,56 @@
         <v>45314</v>
       </c>
       <c r="E8" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="I8">
         <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>228</v>
+      <c r="A9" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1">
-        <v>45677</v>
+        <v>45311</v>
       </c>
       <c r="D9" s="1">
-        <v>45681</v>
+        <v>45315</v>
       </c>
       <c r="E9" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>229</v>
+      <c r="A10" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C10" s="1">
         <v>45314</v>
@@ -3428,85 +3405,85 @@
         <v>45317</v>
       </c>
       <c r="E10" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I10">
         <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>230</v>
+      <c r="A11" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1">
-        <v>45683</v>
+        <v>45317</v>
       </c>
       <c r="D11" s="1">
-        <v>45686</v>
+        <v>45320</v>
       </c>
       <c r="E11" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
         <v>17</v>
       </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="I11">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>231</v>
+      <c r="A12" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1">
-        <v>45325</v>
+        <v>45691</v>
       </c>
       <c r="D12" s="1">
-        <v>45321</v>
+        <v>45694</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="I12">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>232</v>
+      <c r="A13" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1">
         <v>45694</v>
@@ -3515,56 +3492,56 @@
         <v>45697</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I13">
         <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>233</v>
+      <c r="A14" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C14" s="1">
-        <v>45331</v>
+        <v>45697</v>
       </c>
       <c r="D14" s="1">
-        <v>45335</v>
+        <v>45701</v>
       </c>
       <c r="E14" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I14">
         <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>234</v>
+      <c r="A15" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C15" s="1">
         <v>45699</v>
@@ -3573,56 +3550,56 @@
         <v>45703</v>
       </c>
       <c r="E15" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H15" t="s">
-        <v>100</v>
+        <v>205</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>235</v>
+      <c r="A16" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C16" s="1">
-        <v>45337</v>
+        <v>45703</v>
       </c>
       <c r="D16" s="1">
-        <v>45340</v>
+        <v>45706</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H16" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="I16">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>236</v>
+      <c r="A17" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C17" s="1">
         <v>45707</v>
@@ -3631,114 +3608,114 @@
         <v>45710</v>
       </c>
       <c r="E17" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I17">
         <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>237</v>
+      <c r="A18" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C18" s="1">
-        <v>45343</v>
+        <v>45709</v>
       </c>
       <c r="D18" s="1">
-        <v>45346</v>
+        <v>45712</v>
       </c>
       <c r="E18" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>238</v>
+      <c r="A19" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C19" s="1">
         <v>45712</v>
       </c>
       <c r="D19" s="1">
-        <v>45713</v>
+        <v>45715</v>
       </c>
       <c r="E19" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="I19">
         <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>239</v>
+      <c r="A20" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C20" s="1">
-        <v>45349</v>
+        <v>45715</v>
       </c>
       <c r="D20" s="1">
-        <v>45353</v>
+        <v>45718</v>
       </c>
       <c r="E20" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>240</v>
+      <c r="A21" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C21" s="1">
         <v>45717</v>
@@ -3747,16 +3724,16 @@
         <v>45720</v>
       </c>
       <c r="E21" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="I21">
         <v>140</v>
@@ -3764,6 +3741,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
